--- a/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBar.xlsx
+++ b/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBar.xlsx
@@ -360,29 +360,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="0">
+      <x:c r="A1">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="0">
+      <x:c r="A2">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="0">
+      <x:c r="A3">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="0">
+      <x:c r="A4">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -396,22 +393,18 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3cc20586-5dbb-45fc-9f17-8e0cd434b803}</x14:id>
+          <x14:id>{4f54d92e-f4db-4014-9923-df0d6db408f9}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3cc20586-5dbb-45fc-9f17-8e0cd434b803}">
-            <x14:dataBar minLength="0" maxLength="100" showValue="0" gradient="1">
+          <x14:cfRule type="dataBar" id="{4f54d92e-f4db-4014-9923-df0d6db408f9}">
+            <x14:dataBar minLength="0" maxLength="100" showValue="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
               </x14:cfvo>
